--- a/data/trans_orig/IP13_R1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R1_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>528</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48557</t>
+          <t>48979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54193</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110807</t>
+          <t>110906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116136</t>
+          <t>116154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9889</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449805</t>
+          <t>449793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457836</t>
+          <t>457730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498047</t>
+          <t>497125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510263</t>
+          <t>510283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952066</t>
+          <t>952641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>966681</t>
+          <t>966616</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140433</t>
+          <t>140734</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148359</t>
+          <t>148248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178295</t>
+          <t>178067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>322520</t>
+          <t>322307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330455</t>
+          <t>330441</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,47 +1774,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6812</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19822</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11864</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6848</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19006</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31461</t>
+          <t>31232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>646930</t>
+          <t>647066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>658015</t>
+          <t>657930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,49 +1887,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>749384</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>741426</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>754436</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>749384</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>742242</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>754400</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1885</t>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393710</t>
+          <t>1393939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1410473</t>
+          <t>1409589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_R1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R1_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2176</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5699</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>52502</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48979</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54151</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>44747</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>114506</t>
+          <t>101479</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110906</t>
+          <t>98108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116154</t>
+          <t>102849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10522</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5784</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16988</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4703</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9901</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4724</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1857</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9350</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11025</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6336</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>19494</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23672</t>
+          <t>23700</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>465156</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>458690</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>469894</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>635</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>454991</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>449793</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>457730</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>426878</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>422252</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>429745</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>505594</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>497125</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>510283</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,23%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1276</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>960585</t>
+          <t>892034</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952641</t>
+          <t>883580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>966616</t>
+          <t>897593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4431</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3701</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8817</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>167006</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>163451</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>145850</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>140734</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148248</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>181786</t>
+          <t>146173</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178067</t>
+          <t>141345</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>148573</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>327637</t>
+          <t>313179</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>322307</t>
+          <t>308224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330441</t>
+          <t>315898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>18149</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31232</t>
+          <t>31781</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>688895</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>681246</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>693830</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>925</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>653344</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>647066</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>657930</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>749384</t>
+          <t>617798</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>741426</t>
+          <t>610187</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754436</t>
+          <t>621963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1402728</t>
+          <t>1306693</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393939</t>
+          <t>1296848</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1409589</t>
+          <t>1313481</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
